--- a/KURIKULUM2026_REVISI/009C_CPL_PENGETAHUAN_SISTEKIN.xlsx
+++ b/KURIKULUM2026_REVISI/009C_CPL_PENGETAHUAN_SISTEKIN.xlsx
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Ujian Teori Kalkulus, Aljabar Linear, Logika Informatika.</t>
+          <t>Ujian Teori Kalkulus, Aljabar Linear, Matematika Diskrit dan Logika.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Ujian Praktikum Struktur Data &amp; Matematika Diskrit.</t>
+          <t>Ujian Praktikum Struktur Data &amp; Matematika Diskrit dan Logika.</t>
         </is>
       </c>
     </row>
